--- a/DATA/분위수별_회귀분석결과_변동성.xlsx
+++ b/DATA/분위수별_회귀분석결과_변동성.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="종가_수익률" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시가_수익률" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="장중전략_성과" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,78 +427,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Quantile</t>
+          <t>분위수</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N_관측치</t>
+          <t>관측치 수</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>일별변동성_구간</t>
+          <t>Vol_N(일간%) 구간</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>연환산변동성_구간</t>
+          <t>Vol_N(연환산%) 구간</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>절편</t>
+          <t>Vol_N 평균(일간%)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>기울기</t>
+          <t>Vol_N 평균(연환산%)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>t_통계량</t>
+          <t>상수(Intercept)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>p_value</t>
+          <t>p_상수</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>유의여부_5pct</t>
+          <t>Beta_ESI_pos(양변화)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>R_squared</t>
+          <t>p_ESI_pos</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>상관계수_R</t>
+          <t>Beta_ESI_neg(음변화)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>잔차표준오차</t>
+          <t>p_ESI_neg</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>평균수익률_pct</t>
+          <t>R²</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>수익률표준편차_pct</t>
+          <t>Adj_R²</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F통계량</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>F_p값</t>
         </is>
       </c>
     </row>
@@ -511,45 +523,49 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[0.450%, 0.850%]</t>
+          <t>[0.393%, 0.779%]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[7.1%, 13.5%]</t>
+          <t>[6.2%, 12.4%]</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-0.000152</v>
+        <v>0.6446</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.6e-05</v>
+        <v>10.23</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5254</v>
+        <v>0.000173</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5997</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.7925</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-3.4e-05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009</v>
+        <v>0.7966</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0303</v>
+        <v>4.5e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008852</v>
+        <v>0.7803</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0158</v>
+        <v>0.0004</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8842</v>
+        <v>-0.0063</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.9447</v>
       </c>
     </row>
     <row r="3">
@@ -563,45 +579,49 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[0.851%, 1.032%]</t>
+          <t>[0.780%, 0.954%]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[13.5%, 16.4%]</t>
+          <t>[12.4%, 15.1%]</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-0.000335</v>
+        <v>0.8606</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.000118</v>
+        <v>13.66</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.9802999999999999</v>
+        <v>-0.001496</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3277</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0397</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.1e-05</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0032</v>
+        <v>0.6742</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0566</v>
+        <v>-0.00046</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01157</v>
+        <v>0.0055</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0297</v>
+        <v>0.0262</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1569</v>
+        <v>0.0197</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.0085</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0191</v>
       </c>
     </row>
     <row r="4">
@@ -615,45 +635,49 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[1.033%, 1.223%]</t>
+          <t>[0.955%, 1.212%]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[16.4%, 19.4%]</t>
+          <t>[15.2%, 19.2%]</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-3.2e-05</v>
+        <v>1.0844</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.1e-05</v>
+        <v>17.21</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6074000000000001</v>
+        <v>0.001655</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5441</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.091</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1.9e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0012</v>
+        <v>0.9429</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0351</v>
+        <v>0.000354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.012155</v>
+        <v>0.1569</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0052</v>
+        <v>0.0072</v>
       </c>
       <c r="N4" t="n">
-        <v>1.2142</v>
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.0874</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3384</v>
       </c>
     </row>
     <row r="5">
@@ -663,49 +687,541 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>302</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[1.212%, 3.868%]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[19.2%, 61.4%]</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1.5432</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001885</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-9.500000000000001e-05</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7382</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.1e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9782999999999999</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.9396</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>분위수</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>관측치 수</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Vol_N(일간%) 구간</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Vol_N(연환산%) 구간</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Vol_N 평균(일간%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Vol_N 평균(연환산%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>상수(Intercept)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>p_상수</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Beta_ESI_pos(양변화)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p_ESI_pos</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Beta_ESI_neg(음변화)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>p_ESI_neg</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Adj_R²</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>F통계량</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>F_p값</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>302</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[0.393%, 0.779%]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[6.2%, 12.4%]</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6446</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.000462</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-3.1e-05</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.000198</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>301</v>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[0.780%, 0.954%]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[12.4%, 15.1%]</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8606</v>
+      </c>
+      <c r="F3" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.001778</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.000103</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6559</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.00044</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0497</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.5274</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>301</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[0.955%, 1.212%]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[15.2%, 19.2%]</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1.0844</v>
+      </c>
+      <c r="F4" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.002372</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.07480000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.000342</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000603</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.6584</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1922</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>302</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[1.225%, 4.845%]</t>
+          <t>[1.212%, 3.868%]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[19.4%, 76.9%]</t>
+          <t>[19.2%, 61.4%]</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.002952</v>
+        <v>1.5432</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000341</v>
+        <v>24.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3823</v>
+        <v>0.00217</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1679</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1544</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-8.1e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0063</v>
+        <v>0.8299</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07969999999999999</v>
+        <v>-2.1e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.018304</v>
+        <v>0.9704</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2926</v>
+        <v>0.0002</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8332</v>
+        <v>-0.0065</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.9729</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>분위수</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>관측치 수</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Vol_N 연환산% 평균</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>승 횟수</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>패 횟수</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>승률</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>평균 수익률</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>이항검정 p값</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>302</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="D2" t="n">
+        <v>156</v>
+      </c>
+      <c r="E2" t="n">
+        <v>146</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5165999999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.000953</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3023</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="D3" t="n">
+        <v>156</v>
+      </c>
+      <c r="E3" t="n">
+        <v>145</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.00069</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2822</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>301</v>
+      </c>
+      <c r="C4" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="D4" t="n">
+        <v>153</v>
+      </c>
+      <c r="E4" t="n">
+        <v>148</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.000306</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4089</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>302</v>
+      </c>
+      <c r="C5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>142</v>
+      </c>
+      <c r="E5" t="n">
+        <v>160</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.000141</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8629</v>
       </c>
     </row>
   </sheetData>
